--- a/data/trans_camb/KIDM_C_3_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_C_3_R-Provincia-trans_camb.xlsx
@@ -614,7 +614,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,22</t>
+          <t>0,0; 22,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,85; 23,21</t>
+          <t>2,43; 23,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 21,35</t>
+          <t>2,73; 20,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,25; 20,81</t>
+          <t>2,36; 21,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,24; 16,13</t>
+          <t>2,94; 16,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 16,7</t>
+          <t>3,8; 16,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -830,7 +830,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 18,72</t>
+          <t>-0,04; 20,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 2,15</t>
+          <t>-11,31; 2,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 5,48</t>
+          <t>-10,07; 6,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 15,23</t>
+          <t>-3,39; 15,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 4,82</t>
+          <t>-8,02; 5,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 1,69</t>
+          <t>-9,75; 2,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 13,92</t>
+          <t>0,78; 14,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 2,06</t>
+          <t>-6,92; 2,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 2,01</t>
+          <t>-7,96; 1,68</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,42; 895,37</t>
+          <t>-10,98; 1057,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 183,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-56,01; 727,22</t>
+          <t>-51,8; 603,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 329,75</t>
+          <t>-100,0; 300,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,24 +1029,24 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 466,11</t>
+          <t>-0,17; 433,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-84,98; 93,41</t>
+          <t>-87,98; 94,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-89,9; 82,06</t>
+          <t>-90,78; 80,32</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 21,79</t>
+          <t>-1,09; 22,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 0,0</t>
+          <t>-10,96; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 27,24</t>
+          <t>0,51; 26,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,24</t>
+          <t>0,0; 13,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,27</t>
+          <t>0,0; 11,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,94</t>
+          <t>0,0; 15,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 12,34</t>
+          <t>0,15; 13,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 2,37</t>
+          <t>-4,32; 2,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 16,04</t>
+          <t>1,56; 16,51</t>
         </is>
       </c>
     </row>
@@ -1325,27 +1325,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 13,85</t>
+          <t>-3,45; 13,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 20,96</t>
+          <t>-2,53; 19,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 0,0</t>
+          <t>-10,51; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,3</t>
+          <t>0,0; 11,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,5; 25,79</t>
+          <t>5,42; 25,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,24; 10,18</t>
+          <t>-0,22; 9,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 17,67</t>
+          <t>3,1; 17,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 0,0</t>
+          <t>-5,1; 0,0</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,64; —</t>
+          <t>-55,42; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>54,07; —</t>
+          <t>19,83; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,27 +1541,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,97</t>
+          <t>0,0; 26,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 34,79</t>
+          <t>3,48; 33,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,1</t>
+          <t>0,0; 22,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,2; 29,08</t>
+          <t>3,2; 29,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,62; 39,38</t>
+          <t>12,34; 39,57</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,21; 20,57</t>
+          <t>3,19; 18,94</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>10,46; 30,4</t>
+          <t>11,15; 30,46</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,22</t>
+          <t>0,0; 9,0</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1757,22 +1757,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 13,45</t>
+          <t>-4,53; 14,38</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 13,26</t>
+          <t>-4,2; 13,03</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 13,81</t>
+          <t>-5,78; 14,05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,83</t>
+          <t>0,0; 22,81</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,34</t>
+          <t>0,0; 18,14</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,52; 14,29</t>
+          <t>-0,21; 14,44</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 7,82</t>
+          <t>-1,89; 7,17</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 11,14</t>
+          <t>-2,21; 9,44</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1910,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 17,43</t>
+          <t>-0,45; 17,76</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 10,68</t>
+          <t>-4,29; 9,83</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 7,9</t>
+          <t>-6,83; 7,08</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 1,16</t>
+          <t>-13,34; 0,94</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 6,24</t>
+          <t>-10,3; 6,23</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 2,84</t>
+          <t>-11,81; 2,62</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 7,02</t>
+          <t>-4,59; 6,85</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 5,48</t>
+          <t>-5,15; 5,85</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 2,58</t>
+          <t>-7,39; 2,73</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-32,86; 1305,73</t>
+          <t>-36,01; 1533,67</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-81,45; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2094,32 +2094,32 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 108,95</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-90,04; 258,63</t>
+          <t>-86,64; 173,42</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 246,01</t>
+          <t>-100,0; 168,54</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-50,13; 186,47</t>
+          <t>-54,39; 200,48</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-61,79; 164,6</t>
+          <t>-63,69; 217,71</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-91,59; 148,44</t>
+          <t>-92,56; 137,65</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>9,94; 29,66</t>
+          <t>9,76; 29,6</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 16,87</t>
+          <t>-1,98; 16,12</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-18,37; -5,07</t>
+          <t>-17,45; -4,81</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>10,01; 29,0</t>
+          <t>9,36; 28,52</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>3,84; 22,39</t>
+          <t>3,46; 21,87</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-12,75; -1,88</t>
+          <t>-13,75; -2,04</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>11,73; 25,63</t>
+          <t>12,33; 26,18</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,43; 16,69</t>
+          <t>3,3; 16,11</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-13,59; -4,86</t>
+          <t>-13,73; -5,32</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>47,99; 390,81</t>
+          <t>52,23; 413,92</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-15,14; 225,54</t>
+          <t>-15,35; 206,14</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -31,06</t>
+          <t>-100,0; -28,78</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>74,42; 710,55</t>
+          <t>65,75; 668,61</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>26,55; 532,92</t>
+          <t>24,37; 547,83</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 118,21</t>
+          <t>-100,0; 98,63</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>85,49; 363,02</t>
+          <t>89,47; 368,78</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>24,25; 227,58</t>
+          <t>25,19; 217,61</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -50,98</t>
+          <t>-100,0; -56,31</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>5,8; 13,84</t>
+          <t>5,73; 14,1</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,59; 7,06</t>
+          <t>0,07; 6,93</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 1,59</t>
+          <t>-4,67; 1,92</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4,44; 11,2</t>
+          <t>4,41; 10,81</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,58; 9,44</t>
+          <t>2,93; 9,14</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 0,24</t>
+          <t>-4,45; 0,2</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,11; 11,18</t>
+          <t>6,32; 11,51</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2,68; 7,24</t>
+          <t>2,67; 7,25</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -0,14</t>
+          <t>-3,81; -0,08</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>74,14; 337,35</t>
+          <t>76,44; 371,89</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>4,81; 178,07</t>
+          <t>0,07; 172,09</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-71,18; 42,34</t>
+          <t>-69,66; 54,38</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>77,78; 391,32</t>
+          <t>76,31; 381,76</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>47,93; 331,01</t>
+          <t>51,34; 318,32</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-82,65; 15,25</t>
+          <t>-83,69; 18,19</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>102,56; 295,18</t>
+          <t>107,26; 303,67</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>42,07; 190,47</t>
+          <t>49,16; 186,77</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-69,57; -2,86</t>
+          <t>-68,43; 0,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/KIDM_C_3_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_C_3_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,12 +677,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,07</t>
+          <t>0,0; 21,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 23,85</t>
+          <t>2,58; 23,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 20,81</t>
+          <t>2,03; 19,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,36; 21,42</t>
+          <t>2,4; 21,73</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 16,32</t>
+          <t>3,01; 16,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,8; 16,84</t>
+          <t>3,77; 17,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 20,49</t>
+          <t>-0,14; 20,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 2,17</t>
+          <t>-10,7; 2,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,07; 6,25</t>
+          <t>-10,18; 5,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 15,43</t>
+          <t>-3,16; 14,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 5,04</t>
+          <t>-7,91; 4,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 2,05</t>
+          <t>-9,17; 2,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 14,02</t>
+          <t>0,67; 14,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 2,05</t>
+          <t>-7,18; 1,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 1,68</t>
+          <t>-7,21; 1,89</t>
         </is>
       </c>
     </row>
@@ -999,27 +999,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 1057,92</t>
+          <t>-24,81; 997,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 183,22</t>
+          <t>-100,0; 296,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 225,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,8; 603,16</t>
+          <t>-52,31; 798,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 300,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 433,33</t>
+          <t>3,71; 482,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-87,98; 94,76</t>
+          <t>-86,62; 79,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-90,78; 80,32</t>
+          <t>-90,2; 68,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 22,33</t>
+          <t>-1,7; 21,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 0,0</t>
+          <t>-11,64; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 26,16</t>
+          <t>0,95; 27,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,88</t>
+          <t>0,0; 15,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,37</t>
+          <t>0,0; 12,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,76</t>
+          <t>0,0; 16,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 13,0</t>
+          <t>0,06; 11,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 2,4</t>
+          <t>-5,11; 2,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 16,51</t>
+          <t>1,48; 16,45</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 13,53</t>
+          <t>-2,99; 13,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 19,1</t>
+          <t>-1,37; 20,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,72</t>
+          <t>0,0; 11,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,42; 25,03</t>
+          <t>5,68; 25,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 9,37</t>
+          <t>0,09; 10,19</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,1; 17,16</t>
+          <t>3,3; 17,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,0</t>
+          <t>-5,88; 0,0</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-55,42; —</t>
+          <t>-64,47; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>19,83; —</t>
+          <t>29,41; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,27 +1541,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,31</t>
+          <t>0,0; 18,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,48; 33,18</t>
+          <t>3,58; 35,61</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,12</t>
+          <t>0,0; 17,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,2; 29,2</t>
+          <t>3,23; 29,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>12,34; 39,57</t>
+          <t>12,14; 39,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,19; 18,94</t>
+          <t>3,17; 19,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11,15; 30,46</t>
+          <t>10,92; 30,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,0</t>
+          <t>0,0; 7,57</t>
         </is>
       </c>
     </row>
@@ -1757,22 +1757,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 14,38</t>
+          <t>-5,56; 13,54</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 13,03</t>
+          <t>-5,83; 13,77</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 14,05</t>
+          <t>-5,69; 15,96</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,81</t>
+          <t>0,0; 25,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,14</t>
+          <t>0,0; 15,51</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 14,44</t>
+          <t>0,47; 15,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 7,17</t>
+          <t>-2,65; 7,23</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 9,44</t>
+          <t>-1,61; 10,23</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 17,76</t>
+          <t>-0,19; 18,05</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 9,83</t>
+          <t>-3,97; 10,49</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 7,08</t>
+          <t>-6,78; 8,18</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 0,94</t>
+          <t>-12,44; 1,19</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,3; 6,23</t>
+          <t>-9,28; 6,2</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-11,81; 2,62</t>
+          <t>-11,77; 2,32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 6,85</t>
+          <t>-4,56; 7,36</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 5,85</t>
+          <t>-5,44; 5,72</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 2,73</t>
+          <t>-8,3; 2,17</t>
         </is>
       </c>
     </row>
@@ -2079,12 +2079,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-36,01; 1533,67</t>
+          <t>-35,33; 1277,08</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-81,45; —</t>
+          <t>-75,1; —</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2094,32 +2094,32 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 108,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-86,64; 173,42</t>
+          <t>-82,41; 238,71</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 168,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-54,39; 200,48</t>
+          <t>-55,09; 214,81</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-63,69; 217,71</t>
+          <t>-62,86; 184,97</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-92,56; 137,65</t>
+          <t>-90,41; 148,8</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>9,76; 29,6</t>
+          <t>9,02; 30,42</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 16,12</t>
+          <t>-2,65; 16,03</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-17,45; -4,81</t>
+          <t>-17,15; -4,32</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9,36; 28,52</t>
+          <t>9,95; 28,11</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>3,46; 21,87</t>
+          <t>3,73; 21,93</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-13,75; -2,04</t>
+          <t>-13,2; -2,3</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,33; 26,18</t>
+          <t>12,36; 26,59</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>3,3; 16,11</t>
+          <t>3,28; 16,46</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-13,73; -5,32</t>
+          <t>-13,65; -4,67</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>52,23; 413,92</t>
+          <t>53,64; 411,12</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 206,14</t>
+          <t>-16,7; 222,19</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -28,78</t>
+          <t>-100,0; -28,93</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>65,75; 668,61</t>
+          <t>78,11; 630,09</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>24,37; 547,83</t>
+          <t>28,88; 463,26</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 98,63</t>
+          <t>-100,0; 27,52</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>89,47; 368,78</t>
+          <t>92,15; 380,56</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>25,19; 217,61</t>
+          <t>23,14; 232,79</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -56,31</t>
+          <t>-100,0; -54,42</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>5,73; 14,1</t>
+          <t>6,09; 13,98</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,07; 6,93</t>
+          <t>0,29; 7,27</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 1,92</t>
+          <t>-4,77; 1,91</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4,41; 10,81</t>
+          <t>4,04; 11,12</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,93; 9,14</t>
+          <t>2,88; 9,25</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,2</t>
+          <t>-4,44; 0,12</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>6,32; 11,51</t>
+          <t>6,02; 11,13</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,25</t>
+          <t>2,42; 7,14</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,81; -0,08</t>
+          <t>-3,98; 0,02</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>76,44; 371,89</t>
+          <t>83,17; 370,88</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>0,07; 172,09</t>
+          <t>3,71; 191,03</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-69,66; 54,38</t>
+          <t>-70,81; 51,31</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>76,31; 381,76</t>
+          <t>72,29; 394,95</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>51,34; 318,32</t>
+          <t>51,27; 320,67</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-83,69; 18,19</t>
+          <t>-83,33; 17,62</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>107,26; 303,67</t>
+          <t>101,83; 290,03</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>49,16; 186,77</t>
+          <t>38,93; 186,75</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-68,43; 0,61</t>
+          <t>-69,97; 1,1</t>
         </is>
       </c>
     </row>
